--- a/AAII_Financials/Quarterly/KT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>KT</t>
   </si>
@@ -656,299 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4313500</v>
+      </c>
+      <c r="E8" s="3">
         <v>4453000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4741900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5073100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5488000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4648100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4451300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5066700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4750700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4951500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5157200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4975200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4971200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4942000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4937200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4728400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4797200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4771100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4967700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4663000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9042800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4461800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4593400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4620900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4524900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4898600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5266200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5530200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5366700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5309300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5035400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4818300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4877800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4796600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5373800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5127400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5141400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5050500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5419000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4976900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -979,11 +986,11 @@
       <c r="L9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3">
         <v>6238600</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>10</v>
@@ -991,208 +998,214 @@
       <c r="P9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3">
         <v>1926000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1766300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1806600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1690300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2154900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1827600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3430700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1693900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1944000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1823200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1770900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1961600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2367800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2359000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2183800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2066000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2127500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1912300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1924900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1895100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2270400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1989600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1975300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1942800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2260300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1859500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4313500</v>
+      </c>
+      <c r="E10" s="3">
         <v>4453000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4741900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5073100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5488000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4648100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4451300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5066700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4750700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4951500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1081400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4975200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4971200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4942000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3011200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2962000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2990600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3080800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2812800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2835400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5612100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2767900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2649400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2797700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2754000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2937000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2898300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3171200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3182900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3243300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2907900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2906000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2952900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2901500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3103300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3137800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3166000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3107700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3158700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>3117500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E12" s="3">
         <v>42400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>-107700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>39200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>-93900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>48700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>37300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>31700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>30800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>29800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>30500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>32300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>59900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>29700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>28300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>32800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>27800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>33600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>37600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>35900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>35500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>36400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>41200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>35600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>33900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>36400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>42300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>35600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>33400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>38100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>38500</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E14" s="3">
         <v>7700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>116900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>232900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>23700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>201000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-185700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-26500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-41500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-21900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-26500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-21000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-49700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>174600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>67600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-20600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-39800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>22700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-7500</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>1300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>49200</v>
       </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>607700</v>
+      </c>
+      <c r="E15" s="3">
         <v>628900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>671900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>687400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>721100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>657800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>658700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>734500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>701100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>724500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2938200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>696700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>705500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>712800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>697000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>662000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>705300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>677700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>685500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>671400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1348800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>666900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>670400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>697100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>701600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>766400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>783400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>798700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>794700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>825800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>682500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>660500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>690500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>698700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>734900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>737300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>740100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>765600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>764700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>751300</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3899600</v>
+      </c>
+      <c r="E17" s="3">
         <v>4139200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4588900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4693600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4740800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4183400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4898400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4713200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4400300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4582000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4952300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4743200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4539600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4572200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4638000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4371200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4406800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4272900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4664100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4355300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8303100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4108400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4644500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4364600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4225900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4551100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5200500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5231500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5073200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4946500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4977600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4517500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4542500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4463000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5248600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4795400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4749100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4674800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5264400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4615500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>413900</v>
+      </c>
+      <c r="E18" s="3">
         <v>313900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>152900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>379500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>747200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>464700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-447200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>353500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>350300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>369500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>204900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>231900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>431600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>369700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>299300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>357100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>390500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>498200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>303600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>307800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>739700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>353400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-51100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>256300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>299000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>347600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>65600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>298600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>293500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>362700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>57800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>335300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>333600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>125200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>332000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>392300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>375700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>154500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>361400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-71100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-52700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-20800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-30800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-78200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-43800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>23000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-25200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>18000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>70000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>35900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>133100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>96800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>41000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>84500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>39000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>20900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>25900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>66300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>21300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>22500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>54100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>28400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-155400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>9200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-47000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-21400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>64100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-5800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1055700</v>
+      </c>
+      <c r="E21" s="3">
         <v>978200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>896000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1119600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1471300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1143200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>216300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1118800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1129700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1118200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3144500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>972400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1130300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1059600</v>
       </c>
-      <c r="Q21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1045100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1866600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1549800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1128900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1087500</v>
       </c>
-      <c r="W21" s="3" t="s">
+      <c r="X21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1068400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>709600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>997500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1002700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1141300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>896000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1100200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1114100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1254800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>780200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1005600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1093400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1075700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>720500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1096000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1100900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1135700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>998700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1123600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E22" s="3">
         <v>61900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>64300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>60000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>70800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>63200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>65400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>63300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>66100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>77300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>274800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>66300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>70000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>60400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>69100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>54700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>46000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>56300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>47900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>93400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>44000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>53500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>54500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>48300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>61000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>69900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>67100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>68600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>52600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>60800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>65400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>69700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>62500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>67300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>68200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>64100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>417200</v>
+      </c>
+      <c r="E23" s="3">
         <v>336700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>95500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>422400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>720400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>483400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-683700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>387600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>404000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>393600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>260200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>416200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>335600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>204900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>320500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>410200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>488100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>380400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>360200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>743100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>346400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>241900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>238200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>309000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>240500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>249600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>361900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>270600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>328600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>296500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-100000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>278700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>278000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>286200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>154500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>279700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E24" s="3">
         <v>81600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>32200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>105500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>178600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>98500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-162800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>95900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>106100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>101200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>87800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>98100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>22900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>82300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>134000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>142000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>106900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>220200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>104800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-39600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>64900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>77200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>118100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>29600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>50700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>70900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>125500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>76600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>92900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>108300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>8700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>100400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>50900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>84300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>70800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>68700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>310300</v>
+      </c>
+      <c r="E26" s="3">
         <v>255100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>63300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>317000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>541800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>384900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-521000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>291700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>297900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>292400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-32100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>214200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>328400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>237500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>182000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>238100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>276200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>346100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>318300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>253300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>522900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>241600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>177000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>161000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>190900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>189800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>178700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>236400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>194000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>235800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>188200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-108700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>178300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>227100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>201900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>83700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>231400</v>
+        <v>284000</v>
       </c>
       <c r="E27" s="3">
+        <v>231200</v>
+      </c>
+      <c r="F27" s="3">
         <v>77200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>278500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>508100</v>
       </c>
-      <c r="H27" s="3">
-        <v>366600</v>
-      </c>
       <c r="I27" s="3">
+        <v>366400</v>
+      </c>
+      <c r="J27" s="3">
         <v>-444000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>271900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>285000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>279200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>196100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>299300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>227300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>181500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>217200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>238000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>311500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>302900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>232700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>480300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>223900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>51600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>156500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>137100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>175500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>168900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>153100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>210300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>180200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>210900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>165400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-110900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>158300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>195500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>180700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>153300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3248,8 +3309,8 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>10</v>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>10</v>
@@ -3266,14 +3327,17 @@
       <c r="AN29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AO29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP29" s="3">
         <v>-78100</v>
       </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AQ29" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E32" s="3">
         <v>35400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>71100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>52700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>20800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>30800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>78200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>43800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>25200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-18000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-70000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-35900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-133100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-96800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-84500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-20900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-66300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-22500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-54100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-28400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>155400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-9200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>47000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>21400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-64100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>284200</v>
+      </c>
+      <c r="E33" s="3">
         <v>231400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>77400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>278700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>508300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>366600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-443800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>272100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>285200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>279400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>196300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>299600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>227500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>181500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>217200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>238000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>311500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>302900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>232700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>480300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>223900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>51600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>156500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>137100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>175500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>168900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>153100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>210300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>15100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>180200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>210900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>165400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-110900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>158300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>195500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>180700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>75200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>284200</v>
+      </c>
+      <c r="E35" s="3">
         <v>231400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>77400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>278700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>508300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>366600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-443800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>272100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>285200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>279400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>196300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>299600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>227500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>181500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>217200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>238000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>311500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>302900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>232700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>480300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>223900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>51600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>156500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>137100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>175500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>168900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>153100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>210300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>15100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>180200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>210900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>165400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-110900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>158300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>195500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>180700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>75200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1969400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1878900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2429500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2769300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2803700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2127400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2515900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3010400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2748000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2232800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2220600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2310500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1370800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1617700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1836800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2259400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2144500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2038500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2264700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2316700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2322700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2037300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1949600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2303000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2265500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1366700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1960000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1894300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1980100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2516100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2270900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2201600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1889700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1493100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1696800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1908300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1457700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1801900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2610300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1222700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1216800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1048500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>997900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>838700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>881700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>785600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>743200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>885200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1042100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1071000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1116500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>968300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1057000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>991800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>967700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1150200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1068900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>889200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>636300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>820600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>758000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>890100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>870800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>878100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>831200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>738100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>709400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>595900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>912800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>835600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>674200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>722700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>841400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>855900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>668900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>619900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>859000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>648500</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>420600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1950500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2077700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2035300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2299400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2250000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2190700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1977900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2518200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2301400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2663800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5531900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2623200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2297600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2477100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4574700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4129000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4047700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4022100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3820100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4084400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3743400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3816200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3629400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5582900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4377100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4630200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5078400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5468700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5729800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5670300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4881600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6105900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4465800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4537800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5281600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4769800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3934300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5220500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4800000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>4668600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E44" s="3">
         <v>353100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>288300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>315900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>328000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>579800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>636500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>687700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>699600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>669000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>703500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>525500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>483600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>597900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>531900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>493300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>390100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>450600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>385600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>305000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>355600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>438000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>395600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>656000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>493200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>533100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>565700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>566300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>534700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>588300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>574600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>407800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>499300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>601400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>402800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>305100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>369600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>449100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>340200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>328500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4022800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4015200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3878400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4383000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4408900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4038300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3731700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4611100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4378300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4551600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1668700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4953700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3539500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3608500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1575900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1671400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1816000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1684200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1534100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1580600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1529300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1510200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1389400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1533100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1596000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1784000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1770500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1789200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1559600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1592900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1428500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1677100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1407900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1706100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>274600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>579500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>300200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>541700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>280000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>562200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9569300</v>
+      </c>
+      <c r="E46" s="3">
         <v>9541900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9680000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10765600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10629200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9817900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9647600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11570600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11012500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11159300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11195700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11529500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8659900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9358200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9511100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9520800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9548400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9264300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8893800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8923000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8771500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8559700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8254100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10945700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9610000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9145200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10112600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10427900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10400100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11280400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9991200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>11066600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8985400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9179800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8511700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8231600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6681700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8872300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>8679000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>9094700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3594700</v>
+      </c>
+      <c r="E47" s="3">
         <v>3403700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3273100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3198200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3215100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2751200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2748100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3300000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3210000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3132700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3218700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3098900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3057100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3024300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4104900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3834600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3148300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2542100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2401600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2100200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1608400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1664900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1741200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1704500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1597100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1845600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1930400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1979500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1828400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1579500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1460400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1438800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1539400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1533500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1639700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1581700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1544400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1306900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1492000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1351700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9777900</v>
+      </c>
+      <c r="E48" s="3">
         <v>10086800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10943100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10893400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11356600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10599800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10857100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12011800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11522800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11792800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12475000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11839500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12092800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12144500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13489400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12895200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13400500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13092500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13075400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12649700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12372200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12195300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12425900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12164700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12087700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13222900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13974900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13886600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13557500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13558100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11893800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11321200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11868100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12053100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12981600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12757400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12856500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>13521300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>13914100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>13485000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1210100</v>
+      </c>
+      <c r="E49" s="3">
         <v>949000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>961800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1185600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1255000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1219500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1190500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1663600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1644600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1790500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1847100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2178600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2280900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2353400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2347400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2384300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2516200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2551100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2585500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2311900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1946600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1516100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1599300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1938400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2038600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2281600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2408900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2684600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2756800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2960400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2862000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1895500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2058000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2124700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2316800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2523000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2597400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2658100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2720500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2394800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4072200</v>
+      </c>
+      <c r="E52" s="3">
         <v>3989900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4103600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3934200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4089600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3689300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3216500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3354400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3289700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3280000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3393400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3401600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3401900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3294400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1282600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1040700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1076900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>898800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>913300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>888600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>905600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>889300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>889700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>859400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>849300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>914600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>932200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>980000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>910200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>877100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>831200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>720000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>722300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>701900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>713400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>754500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>806500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>733700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>723300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>796100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28854900</v>
+      </c>
+      <c r="E54" s="3">
         <v>28583500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29752700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30618400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31176300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28645700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28349900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32549200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31309400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31779700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32935900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32666600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30185000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30842400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30735500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29675600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29690400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>28348800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27869500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26873400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25604200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24825300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24910300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27612600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>26182600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27410000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29359100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29958500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29453100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30255500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27038600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26442100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25173100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25593000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>26163200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>25848200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>24486400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>27092300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>27529000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>27122200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
         <v>858900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>792700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>815300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>587400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>701800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>921800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1036200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>938700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1152200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>878700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>868300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>862900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1011300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>948300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>977300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1152900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>982200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3485400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>885800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>917400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1253600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>950600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>977300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1109100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1448600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>949800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1067600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1038700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1098400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>941400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1218000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1231400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1075000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1013800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1097900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1112400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1021400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2935500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2844800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1994300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1993700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2430300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2723800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2879700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3596300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2850800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2897600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2596700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1990600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1824100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1943400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1607200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1724600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2351900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1446100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1548100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1450500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>968100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1486900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1304900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1433700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1550700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1360500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1341400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>814900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>513600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1045600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1149500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1147700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1629600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1288800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1384700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1395700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>870000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1482700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1638000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1862000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5564000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4601400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5313200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5892400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5727500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5607700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5810800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6631900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6341700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6615100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6541200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6869600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4785600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4984200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5554400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4990100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5113700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5088000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4853400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4603200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1790800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4488200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4580200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6151600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5129300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5366300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7052500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6613100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7255700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6920200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5697500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6800800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5074300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5420900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5721200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5287100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4518900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6162500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5769200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>5461200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8499500</v>
+      </c>
+      <c r="E60" s="3">
         <v>8305100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8100200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8701300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8957900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8918900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9392300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11150000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10228700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10451400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10138700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10012500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7488400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7795900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8024500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7726100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8413800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7511500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7554300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7036000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6244300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6860900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6802400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8838900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7630600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7704100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8625800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8876700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8719100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9033400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7885700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9046900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7645300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7927600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8337300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7757800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6402700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>8743100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>8519500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>8344600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5210600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5466200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6463300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6255100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6256800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5579700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4959300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4680100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5341500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5492000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6211900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6522700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6654900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7055000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6776800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6726800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6212600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6164500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5649700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5723000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5693500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5090600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4955500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5083600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5131200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5346800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5892300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4888400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4992400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5133400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4435000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4012100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3918200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4330200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4497000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4630700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4871900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5128000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5670700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5550600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>877500</v>
+      </c>
+      <c r="E62" s="3">
         <v>694100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>755200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>856700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>968400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>877100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1005300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1126400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1039100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1067800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1337600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1331300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1097700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1095200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2123200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2151700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2216500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2061500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2240100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2041300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1918600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1523600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1644300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1634600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1583000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1699000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2317100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2637700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2537500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2676700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2343600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1583500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1595300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1566900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1703600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1767100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1724000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1716200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1823400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1826100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15661600</v>
+      </c>
+      <c r="E66" s="3">
         <v>15448900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16273100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16908300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17228100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16193200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16167500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17941100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17534500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17953100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18622400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18759200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16173900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16920700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18276400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17907100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18135500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17006400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16637100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15997400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14992800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14615000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14541800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16778700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15539300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16012700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17745200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17838700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17641400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18239900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15948400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15867400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14413800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>15045800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15762600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>15390700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>14206600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>16775100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17231200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>16916400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9989600</v>
+      </c>
+      <c r="E72" s="3">
         <v>9968800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10366600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10667800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10891200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9640600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9328000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11173300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10488100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10686100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11177400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10823900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10936300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10743600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10693000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10115800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10298700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10058600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9965500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9616300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9379600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8964300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8995000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9347600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9189500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9723100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9888700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10348400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10066200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10255200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9516200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9073800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9217900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9009800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8789800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8849700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8692000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8692100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8690900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>8603800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12000700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11948300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12231000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12422400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12652600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11275100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10973600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13175100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12419800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12464600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12916200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12479900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12615300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12545300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12459100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11768500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11554900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11342500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11232400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10876000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10611400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10210200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10368500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10833900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10643400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11397300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11613900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12119800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11811700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12015600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11090300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10574700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10759300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10547200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10400600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10457500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10279800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10317200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>10297700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>10205800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>284200</v>
+      </c>
+      <c r="E81" s="3">
         <v>231400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>77400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>278700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>508300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>366600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-443800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>272100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>285200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>279400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>196300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>299600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>227500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>181500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>217200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>238000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>311500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>302900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>232700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>480300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>223900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>51600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>156500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>137100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>175500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>168900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>153100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>210300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>15100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>180200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>210900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>165400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-110900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>158300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>195500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>180700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>75200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>618900</v>
+      </c>
+      <c r="E83" s="3">
         <v>565300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>559200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>624100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>590800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>608700</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>590500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>596400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600600</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>539500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>596100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>624700</v>
       </c>
-      <c r="Q83" s="3" t="s">
+      <c r="R83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>670000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1406100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-2083900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>692200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>679400</v>
       </c>
-      <c r="W83" s="3" t="s">
+      <c r="X83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>674000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>676200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>702100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>710000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>772900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>826700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>798700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>794700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>825800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>701100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>682400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>704100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>713700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>750800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>754800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>755600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>781300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>780100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>982500</v>
+      </c>
+      <c r="E89" s="3">
         <v>427100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>686900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>899700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1519200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>428000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>450700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>886000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1540000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>829100</v>
       </c>
-      <c r="M89" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1326600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1338800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>701200</v>
       </c>
-      <c r="Q89" s="3" t="s">
+      <c r="R89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>844200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1559600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3591600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1049700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1128600</v>
       </c>
-      <c r="W89" s="3" t="s">
+      <c r="X89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>860900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>782700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>962700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1160800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>776400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>455100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>834900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1039100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>992600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>582900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1088500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>989800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>667300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>648500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1115200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1171700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>487900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>855200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1062800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-403500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-367300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-619100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-479500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-484500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-932900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-601300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-630200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-467100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-421300</v>
       </c>
-      <c r="M91" s="3" t="s">
+      <c r="N91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-633500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-493800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-798400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1032058000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-778929000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1347605000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1033165000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-963672000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-983353000</v>
       </c>
-      <c r="W91" s="3" t="s">
+      <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-558200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-471300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-485300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-597700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-597300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-312500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-937400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-888300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-750700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-512100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-767200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-924000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-545800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-514000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1169400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-749600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-434100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-357400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-502600</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-966000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-499700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1161700</v>
       </c>
-      <c r="Q94" s="3" t="s">
+      <c r="R94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-628300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2269300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2772600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-991500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1469100</v>
       </c>
-      <c r="W94" s="3" t="s">
+      <c r="X94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-802800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-665000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-671000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-474700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1154900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-987100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-882700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-613600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-943700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-803200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-494600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-177800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-777500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-820800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-931000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-566100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-764400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-996000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-816000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,35 +10500,35 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-362400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="3">
         <v>-100</v>
       </c>
       <c r="Z96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA96" s="3">
         <v>0</v>
@@ -10318,11 +10552,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10339,13 +10573,16 @@
         <v>0</v>
       </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-6900</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-348900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-86600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-287700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-513400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>345400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>133600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-322200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-613100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-237700</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>608600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1069900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>198400</v>
       </c>
-      <c r="Q100" s="3" t="s">
+      <c r="R100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-18300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>556100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>270900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-109100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>333300</v>
       </c>
-      <c r="W100" s="3" t="s">
+      <c r="X100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>28500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-379800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-253900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>326700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-192300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>689200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-61900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-878300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>208100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-214200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-416400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-16200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-37500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>266400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-911600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-529000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-365900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>131800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="J101" s="3">
-        <v>200</v>
       </c>
       <c r="K101" s="3">
         <v>200</v>
       </c>
       <c r="L101" s="3">
+        <v>200</v>
+      </c>
+      <c r="M101" s="3">
         <v>1500</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3" t="s">
+      <c r="R101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1200</v>
       </c>
-      <c r="W101" s="3" t="s">
+      <c r="X101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
       <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
         <v>1800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>2300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-424900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-265500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>68300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>488700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-396300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-160600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>127300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>570400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>90100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>969300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-230600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-260600</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="R102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>199600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-150400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-549000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-52000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6000</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="X102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>87700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-263700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>37500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1012700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-570200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>150900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-108300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-453000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>56000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>379400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>396700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-126600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-211500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>450700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-304200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-808400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-504400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>375800</v>
       </c>
     </row>
